--- a/project2_data/project2.xlsx
+++ b/project2_data/project2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_alldata\Excel\project2_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1788028-4D59-4689-8849-BFD01C6E7773}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625262B4-B069-492A-91AC-AC0D6D50A72C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="4" xr2:uid="{64B39548-4A09-455D-A5FE-B6F60E74160D}"/>
   </bookViews>
@@ -28750,7 +28750,7 @@
       </c>
       <c r="O2" s="29">
         <f ca="1">NOW()</f>
-        <v>46070.880380671297</v>
+        <v>46112.465371412036</v>
       </c>
       <c r="P2" s="31" t="str">
         <f>INDEX($B$2:$B$200,MATCH(MAX($E$2:$E$200),$E$2:$E$200,0))</f>
